--- a/files/港岛-香港仔及鸭脷洲-澄天.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-澄天.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="澄天 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="澄天" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5750,141 +5788,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>澄天 - 澄天 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>澄天 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>110 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>109 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$2,430万
+$2430万
 $27,334/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 896呎 (3房)
 招标单位
@@ -5892,18 +5930,18 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $580万
@@ -5911,7 +5949,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $513万
@@ -5919,7 +5957,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $793万
@@ -5927,7 +5965,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $802万
@@ -5935,7 +5973,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $464万
@@ -5943,7 +5981,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $589万
@@ -5952,13 +5990,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $576万
@@ -5966,7 +6004,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $511万
@@ -5974,7 +6012,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $812万
@@ -5982,7 +6020,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $730万
@@ -5990,7 +6028,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $462万
@@ -5998,7 +6036,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $597万
@@ -6007,13 +6045,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $616万
@@ -6021,7 +6059,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $510万
@@ -6029,7 +6067,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $785万
@@ -6037,7 +6075,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $725万
@@ -6045,7 +6083,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $527万
@@ -6053,7 +6091,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $594万
@@ -6062,13 +6100,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $572万
@@ -6076,7 +6114,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $508万
@@ -6084,7 +6122,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $758万
@@ -6092,7 +6130,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $715万
@@ -6100,7 +6138,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $461万
@@ -6108,7 +6146,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $578万
@@ -6117,13 +6155,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $570万
@@ -6131,7 +6169,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $506万
@@ -6139,7 +6177,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $731万
@@ -6147,7 +6185,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $739万
@@ -6155,7 +6193,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $512万
@@ -6163,7 +6201,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $581万
@@ -6172,13 +6210,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $615万
@@ -6186,7 +6224,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $519万
@@ -6194,7 +6232,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $724万
@@ -6202,7 +6240,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $732万
@@ -6210,7 +6248,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $460万
@@ -6218,7 +6256,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $589万
@@ -6227,13 +6265,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $600万
@@ -6241,7 +6279,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $523万
@@ -6249,7 +6287,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $716万
@@ -6257,7 +6295,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $724万
@@ -6265,7 +6303,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 287呎 (1房)
 $460万
@@ -6273,7 +6311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $650万
@@ -6282,13 +6320,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $570万
@@ -6296,7 +6334,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $521万
@@ -6304,7 +6342,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 399呎 (2房)
 $742万
@@ -6312,7 +6350,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $720万
@@ -6320,7 +6358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $496万
@@ -6328,7 +6366,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $688万
@@ -6337,13 +6375,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $567万
@@ -6351,7 +6389,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $492万
@@ -6359,7 +6397,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $708万
@@ -6367,7 +6405,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $716万
@@ -6375,7 +6413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $493万
@@ -6383,7 +6421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $698万
@@ -6392,13 +6430,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $564万
@@ -6406,7 +6444,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $515万
@@ -6414,7 +6452,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $741万
@@ -6422,7 +6460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $712万
@@ -6430,7 +6468,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $490万
@@ -6438,7 +6476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $694万
@@ -6447,13 +6485,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $560万
@@ -6461,7 +6499,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $512万
@@ -6469,7 +6507,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $729万
@@ -6477,7 +6515,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $707万
@@ -6485,7 +6523,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $487万
@@ -6493,7 +6531,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $675万
@@ -6502,13 +6540,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $586万
@@ -6516,7 +6554,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $504万
@@ -6524,7 +6562,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $732万
@@ -6532,7 +6570,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $703万
@@ -6540,7 +6578,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $484万
@@ -6548,7 +6586,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $686万
@@ -6557,13 +6595,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $577万
@@ -6571,7 +6609,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $495万
@@ -6579,7 +6617,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $691万
@@ -6587,7 +6625,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $699万
@@ -6595,7 +6633,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $481万
@@ -6603,7 +6641,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $695万
@@ -6612,13 +6650,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $551万
@@ -6626,7 +6664,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $462万
@@ -6634,7 +6672,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $687万
@@ -6642,7 +6680,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 399呎 (2房)
 $680万
@@ -6650,7 +6688,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 285呎 (1房)
 $478万
@@ -6658,7 +6696,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $663万
@@ -6667,13 +6705,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $532万
@@ -6681,7 +6719,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $500万
@@ -6689,7 +6727,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 399呎 (2房)
 $712万
@@ -6697,7 +6735,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $676万
@@ -6705,7 +6743,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $435万
@@ -6713,7 +6751,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $694万
@@ -6722,13 +6760,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $531万
@@ -6736,7 +6774,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $477万
@@ -6744,7 +6782,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $699万
@@ -6752,7 +6790,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $659万
@@ -6760,7 +6798,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $449万
@@ -6768,7 +6806,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $670万
@@ -6777,13 +6815,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 325呎 (1房)
 $553万
@@ -6791,7 +6829,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $480万
@@ -6799,7 +6837,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 400呎 (2房)
 $656万
@@ -6807,7 +6845,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 400呎 (2房)
 $677万
@@ -6815,7 +6853,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 286呎 (1房)
 $440万
@@ -6823,7 +6861,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 400呎 (2房)
 $628万
@@ -6832,13 +6870,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 288呎 (1房)
 $576万
@@ -6846,7 +6884,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 247呎 (1房)
 $459万
@@ -6854,7 +6892,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 365呎 (2房)
 $750万
@@ -6862,7 +6900,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 365呎 (2房)
 $730万
@@ -6870,7 +6908,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 245呎 (1房)
 $490万
@@ -6878,7 +6916,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 362呎 (2房)
 $724万
@@ -6889,7 +6927,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
